--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,9 +436,55 @@
         <v xml:space="preserve"> m</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Test User</v>
+      </c>
+      <c r="B3" t="str">
+        <v>test@example.com</v>
+      </c>
+      <c r="C3" t="str">
+        <v>9876543210</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Test Org</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Test Subject</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Test message from email</v>
+      </c>
+      <c r="G3" t="str">
+        <v>1/31/2026, 12:21:27 PM</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Test AMP User</v>
+      </c>
+      <c r="B4" t="str">
+        <v>test@example.com</v>
+      </c>
+      <c r="C4" t="str">
+        <v>9876543210</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Test Org</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Test Subject from Stripo</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Test message from AMP email</v>
+      </c>
+      <c r="G4" t="str">
+        <v>1/31/2026, 12:24:10 PM</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>